--- a/data/produtos.xlsx
+++ b/data/produtos.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,37 +440,19 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>gugus</t>
+          <t>Gustavo</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2026/02/10</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>200</v>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C3" t="n">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>26/03/01</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
